--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pacomini/Development/FCC_Products/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B536CBC1-F871-C847-87F0-F1ECA5A754A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44373440-A264-E64E-803E-8FC720D8060B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1260" yWindow="2380" windowWidth="31960" windowHeight="16680" xr2:uid="{5FF4F24B-2989-174F-B76E-8FA5BFB4FB96}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$B$1:$E$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$C$1:$D$5</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -42,104 +42,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Product_Description</t>
   </si>
   <si>
-    <t>Category</t>
-  </si>
-  <si>
-    <t>半人工關節置換術 (Bipolar)</t>
-  </si>
-  <si>
-    <t>全髋關節置換術 (THR)</t>
-  </si>
-  <si>
-    <t>全膝關節置換術 (TKR)</t>
-  </si>
-  <si>
-    <t>2309053381</t>
-  </si>
-  <si>
-    <t>1503-3XXX Bipolar Cap</t>
-  </si>
-  <si>
-    <t>半人工關節置換術 (Bipolar) / 全髋關節置換術 (THR)</t>
-  </si>
-  <si>
-    <t>2309053373</t>
-  </si>
-  <si>
-    <t>1106-30XX UTF stem, reduced, Ti plasma spray</t>
-  </si>
-  <si>
-    <t>2309053365</t>
-  </si>
-  <si>
-    <t>1203-5XXX Ceramic Femoral Head, Delta, O.D.φ(22, 28, 32, 36)mm</t>
-  </si>
-  <si>
-    <t>2309053390</t>
-  </si>
-  <si>
-    <t>1206-1XXX U2 Femoral head CoCr, Ø22, 26, 28, 32, 36mm</t>
-  </si>
-  <si>
-    <t>2309053322</t>
-  </si>
-  <si>
-    <t>1306-10XX U-Motion II HA Cup, Φ44, 46, 48, 50, 52, 54, 56, 58, 60, 62mm</t>
-  </si>
-  <si>
-    <t>2309053357</t>
-  </si>
-  <si>
-    <t>1406-1XXX U-Motion II Delta Ceramic Liner</t>
-  </si>
-  <si>
-    <t>2309053349</t>
-  </si>
-  <si>
-    <t>1406-5XXX U-Motion II XPE Cup Liner, 20 degrees</t>
-  </si>
-  <si>
-    <t>2309053292</t>
-  </si>
-  <si>
-    <t>2103-1XXX U2 Femoral component, CR, porous coated</t>
-  </si>
-  <si>
     <t>2309053233</t>
   </si>
   <si>
     <t>2103-3XXX Femoral component, PS</t>
   </si>
   <si>
-    <t>2309053241</t>
-  </si>
-  <si>
-    <t>2203-32XX Tibial baseplate, CMA</t>
-  </si>
-  <si>
-    <t>2309053306</t>
-  </si>
-  <si>
-    <t>2203-34XX Tibial baseplate, TPS+</t>
-  </si>
-  <si>
     <t>2309053250</t>
   </si>
   <si>
     <t>2303-36XX XPE Tibial Insert, PS</t>
   </si>
   <si>
-    <t>2309053268</t>
-  </si>
-  <si>
-    <t>2303-38XX U2 E-XPE Tibial Insert (PS) (E-XPS)</t>
-  </si>
-  <si>
     <t>2309053276</t>
   </si>
   <si>
@@ -150,18 +69,6 @@
   </si>
   <si>
     <t>2309053284</t>
-  </si>
-  <si>
-    <t>2309053330</t>
-  </si>
-  <si>
-    <t>5206-1015 Ti Cancellous Screw, Φ 6.5 x XXmm</t>
-  </si>
-  <si>
-    <t>2309053314</t>
-  </si>
-  <si>
-    <t>2303-17XX E-XPE Tibial insert, UC</t>
   </si>
   <si>
     <t>Price</t>
@@ -542,82 +449,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69C910A5-DA5D-8A43-A866-6F8547F5DDB6}">
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="20.33203125" customWidth="1"/>
-    <col min="5" max="5" width="60.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="48.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E1" t="s">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>18495</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>23</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>1950</v>
       </c>
       <c r="D3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E3" t="s">
-        <v>33</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4">
         <v>7300</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -628,239 +522,11 @@
         <v>7300</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6">
-        <v>9735</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7">
-        <v>24850</v>
-      </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8">
-        <v>16150</v>
-      </c>
-      <c r="D8" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
         <v>3</v>
-      </c>
-      <c r="B9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>11320</v>
-      </c>
-      <c r="D9" t="s">
-        <v>38</v>
-      </c>
-      <c r="E9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10">
-        <v>11320</v>
-      </c>
-      <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>772</v>
-      </c>
-      <c r="D11" t="s">
-        <v>36</v>
-      </c>
-      <c r="E11" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>4345</v>
-      </c>
-      <c r="D12" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>13035</v>
-      </c>
-      <c r="D13" t="s">
-        <v>16</v>
-      </c>
-      <c r="E13" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>13520</v>
-      </c>
-      <c r="D14" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>6379</v>
-      </c>
-      <c r="D15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16">
-        <v>1</v>
-      </c>
-      <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16">
-        <v>7726</v>
-      </c>
-      <c r="D16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17">
-        <v>2</v>
-      </c>
-      <c r="B17" t="s">
-        <v>2</v>
-      </c>
-      <c r="C17">
-        <v>11007</v>
-      </c>
-      <c r="D17" t="s">
-        <v>10</v>
-      </c>
-      <c r="E17" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18">
-        <v>4</v>
-      </c>
-      <c r="B18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18">
-        <v>11588</v>
-      </c>
-      <c r="D18" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="B1:E18" xr:uid="{69C910A5-DA5D-8A43-A866-6F8547F5DDB6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:E18">
-      <sortCondition ref="B1:B18"/>
-    </sortState>
-  </autoFilter>
+  <autoFilter ref="C1:D5" xr:uid="{69C910A5-DA5D-8A43-A866-6F8547F5DDB6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>